--- a/medicoes.xlsx
+++ b/medicoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E661"/>
+  <dimension ref="A1:E673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9514,7 +9514,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1674093</t>
+          <t>1671216C</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -9524,24 +9524,24 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>BMD-1674093-HAGAP.pdf</t>
+          <t>BMD-1671216C-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>4.813,55</t>
+          <t>13,51</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1671216I</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -9551,24 +9551,24 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>BMD-1675389-HAGAP.pdf</t>
+          <t>BMD-1671216I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>389,52</t>
+          <t>8.907,02</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1676605</t>
+          <t>1674093</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -9578,24 +9578,24 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>BMD-1676605-HAGAP.pdf</t>
+          <t>BMD-1674093-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>7.052,33</t>
+          <t>4.813,55</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1691390</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -9605,24 +9605,24 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>BMD-1691390-HAGAP..pdf</t>
+          <t>BMD-1675389-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>457,30</t>
+          <t>389,52</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1676605</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -9632,24 +9632,24 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>BMD-1694841-HAGAP.pdf</t>
+          <t>BMD-1676605-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>1.163,67</t>
+          <t>7.052,33</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1691390</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -9659,24 +9659,24 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>BMD-1703223-HAGAP.pdf</t>
+          <t>BMD-1691390-HAGAP..pdf</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>1.471,15</t>
+          <t>457,30</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -9686,24 +9686,24 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>BMD-1704877-HAGAP.pdf</t>
+          <t>BMD-1694841-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>1.223,97</t>
+          <t>1.163,67</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>1704953</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -9713,24 +9713,24 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>BMD-1704953-HAGAP.pdf</t>
+          <t>BMD-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>9.260,98</t>
+          <t>1.471,15</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -9740,24 +9740,24 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>BMD-1708066-HAGAP.pdf</t>
+          <t>BMD-1704877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>1.223,97</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1708908</t>
+          <t>1704953</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -9767,24 +9767,24 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>BMD-1708908-HAGAP.pdf</t>
+          <t>BMD-1704953-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>9.260,98</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -9794,24 +9794,24 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>BMD-1709486-HAGAP.pdf</t>
+          <t>BMD-1708066-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>1.889,02</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>1710287C</t>
+          <t>1708908</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -9821,24 +9821,24 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>BMD-1710287C-HAGAP.pdf</t>
+          <t>BMD-1708908-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>56,80</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1710322</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -9848,24 +9848,24 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>BMD-1710322-HAGAP.pdf</t>
+          <t>BMD-1709486-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>190.028,30</t>
+          <t>1.889,02</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>1711507</t>
+          <t>1710287C</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -9875,24 +9875,24 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>BMD-1711507-HAGAP.pdf</t>
+          <t>BMD-1710287C-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>1.523,84</t>
+          <t>56,80</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1710322</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -9902,24 +9902,24 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>BMD-1711775-HAGAP.pdf</t>
+          <t>BMD-1710322-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>4,07</t>
+          <t>190.028,30</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>1711788</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -9929,24 +9929,24 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>BMD-1711788-HAGAP.pdf</t>
+          <t>BMD-1711507-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>8.104,03</t>
+          <t>1.523,84</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -9956,24 +9956,24 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>BMD-1712530-HAGAP.pdf</t>
+          <t>BMD-1711775-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>1.529,03</t>
+          <t>4,07</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1711788</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -9983,24 +9983,24 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>BMD-1712547-HAGAP.pdf</t>
+          <t>BMD-1711788-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>117,63</t>
+          <t>8.104,03</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -10010,24 +10010,24 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>BMD-1712550-HAGAP.pdf</t>
+          <t>BMD-1712530-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>421,10</t>
+          <t>1.529,03</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -10037,24 +10037,24 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>BMD-1712766-HAGAP.pdf</t>
+          <t>BMD-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>117,63</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -10064,24 +10064,24 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>BMD-1713044II-HAGAP.pdf</t>
+          <t>BMD-1712550-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>421,10</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -10091,24 +10091,24 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>BMD-1713226-HAGAP.pdf</t>
+          <t>BMD-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>237,93</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1713626</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -10118,24 +10118,24 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>BMD-1713626-HAGAP.pdf</t>
+          <t>BMD-1713044II-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>161,42</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1713656I</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -10145,24 +10145,24 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>BMD-1713656I-HAGAP.pdf</t>
+          <t>BMD-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>161,74</t>
+          <t>237,93</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>1713660</t>
+          <t>1713626</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>BMD-1713660-HAGAP.pdf</t>
+          <t>BMD-1713626-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>161,11</t>
+          <t>161,42</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -10189,7 +10189,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>1713681</t>
+          <t>1713656I</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -10199,24 +10199,24 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>BMD-1713681-HAGAP.pdf</t>
+          <t>BMD-1713656I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>344,71</t>
+          <t>161,74</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>1713903C</t>
+          <t>1713660</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -10226,24 +10226,24 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>BMD-1713903C-HAGAP.pdf</t>
+          <t>BMD-1713660-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>36,14</t>
+          <t>161,11</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>1713903I</t>
+          <t>1713681</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -10253,24 +10253,24 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>BMD-1713903I-HAGAP.pdf</t>
+          <t>BMD-1713681-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>972,91</t>
+          <t>344,71</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1713903C</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -10280,24 +10280,24 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>BMD-1714342-HAGAP.pdf</t>
+          <t>BMD-1713903C-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>62,40</t>
+          <t>36,14</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>1714348</t>
+          <t>1713903I</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -10307,24 +10307,24 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>BMD-1714348-HAGAP.pdf</t>
+          <t>BMD-1713903I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>532,46</t>
+          <t>972,91</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>1714699</t>
+          <t>1713916</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -10334,24 +10334,24 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>BMD-1714699-HAGAP.pdf</t>
+          <t>BMD-1713916-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>6.393,67</t>
+          <t>3.083,18</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>1714857</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -10361,12 +10361,12 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>BMD-1714857-HAGAP.pdf</t>
+          <t>BMD-1714342-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>185,07</t>
+          <t>62,40</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -10378,7 +10378,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1714348</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -10388,24 +10388,24 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>BMD-1714909-HAGAP.pdf</t>
+          <t>BMD-1714348-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>107,93</t>
+          <t>532,46</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -10415,24 +10415,24 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>BMD-1715127-HAGAP.pdf</t>
+          <t>BMD-1714699-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>128,31</t>
+          <t>6.393,67</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1714857</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -10442,24 +10442,24 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>BMD-1715131-HAGAP.pdf</t>
+          <t>BMD-1714857-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>185,07</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -10469,24 +10469,24 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>BMD-1715201-HAGAP.pdf</t>
+          <t>BMD-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>3,29</t>
+          <t>107,93</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -10496,24 +10496,24 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>BMD-1715257I-HAGAP.pdf</t>
+          <t>BMD-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>128,31</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -10523,24 +10523,24 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>BMD-1715668-HAGAP.pdf</t>
+          <t>BMD-1715131-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>249,06</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>1715816C</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -10550,24 +10550,24 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>BMD-1715816C-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1715201-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>3,29</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>1715816I</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -10577,24 +10577,24 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>BMD-1715816I-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1715257I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>3.168,40</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>1715899</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -10604,24 +10604,24 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>BMD-1715899-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>3.389,65</t>
+          <t>249,06</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>1715955I</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -10631,24 +10631,24 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>BMD-1715955I-HAGAP.pdf</t>
+          <t>BMD-1715816C-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>1.460,80</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>1717166</t>
+          <t>1715816I</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -10658,24 +10658,24 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>BMD-1717166-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1715816I-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>22.116,83</t>
+          <t>3.168,40</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1715899</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -10685,24 +10685,24 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>BMD-1717168-HAGAP.pdf</t>
+          <t>BMD-1715899-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.389,65</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>1718019</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -10712,24 +10712,24 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>BMD-1718019-HAGAP.pdf</t>
+          <t>BMD-1715955I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>4.408,31</t>
+          <t>1.460,80</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1717166</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -10739,24 +10739,24 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>BMD-1718442-HAGAP.pdf</t>
+          <t>BMD-1717166-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>22.116,83</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>1718555</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -10766,24 +10766,24 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>BMD-1718555-HAGAP.pdf</t>
+          <t>BMD-1717168-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>80,49</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1718019</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -10793,24 +10793,24 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>BMD-1718561-HAGAP PARCIAL.pdf</t>
+          <t>BMD-1718019-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>13.683,99</t>
+          <t>4.408,31</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>1718951</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -10820,24 +10820,24 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>BMD-1718951-HAGAP.pdf</t>
+          <t>BMD-1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>257,86</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1718555</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>BMD-1719070-HAGAP.pdf</t>
+          <t>BMD-1718555-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>333,14</t>
+          <t>80,49</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -10864,7 +10864,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>1719077</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -10874,24 +10874,24 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>BMD-1719077-HAGAP.pdf</t>
+          <t>BMD-1718561-HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2.304,20</t>
+          <t>13.683,99</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>1719154</t>
+          <t>1718951</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -10901,24 +10901,24 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>BMD-1719154-HAGAP.pdf</t>
+          <t>BMD-1718951-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2.574,70</t>
+          <t>257,86</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -10928,24 +10928,24 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>BMD-1719213-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>5.951,32</t>
+          <t>333,14</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>1719214</t>
+          <t>1719077</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -10955,24 +10955,24 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>BMD-1719214-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1719077-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>6.124,60</t>
+          <t>2.304,20</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1719154</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -10982,24 +10982,24 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>BMD-1719881-HAGAP.pdf</t>
+          <t>BMD-1719154-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>2.574,70</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -11009,24 +11009,24 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>BMD-1719881HAGAP.pdf</t>
+          <t>BMD-1719213-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>5.951,32</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1719214</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -11036,24 +11036,24 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>BMD-1720116-HAGAP.pdf</t>
+          <t>BMD-1719214-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>168,95</t>
+          <t>6.124,60</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>1721631</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -11063,24 +11063,24 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>BMD-1721631-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1719881-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>12.649,43</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>1721631C</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -11090,24 +11090,24 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>BMD-1721631C-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1719881HAGAP.pdf</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -11117,24 +11117,24 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>BMD-1721869-HAGAP.pdf</t>
+          <t>BMD-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>133,09</t>
+          <t>168,95</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>1721886</t>
+          <t>1721631</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -11144,24 +11144,24 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>BMD-1721886 - HAGAP PARCIAL.pdf</t>
+          <t>BMD-1721631-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>14.551,70</t>
+          <t>12.649,43</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1721631C</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -11171,24 +11171,24 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>BMD-1724491-HAGAP.pdf</t>
+          <t>BMD-1721631C-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>33,42</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>1724537</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -11198,24 +11198,24 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>BMD-1724537-HAGAP.pdf</t>
+          <t>BMD-1721869-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2.386,57</t>
+          <t>133,09</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>1724551</t>
+          <t>1721886</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -11225,24 +11225,24 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>BMD-1724551-HAGAP.pdf</t>
+          <t>BMD-1721886 - HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>1.387,89</t>
+          <t>14.551,70</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1723726</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -11252,24 +11252,24 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>BMD-1725260-HAGAP.pdf</t>
+          <t>BMD-1723726-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>10,16</t>
+          <t>1.718,28</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>1726320</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -11279,24 +11279,24 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>BMD-1726320-HAGAP.pdf</t>
+          <t>BMD-1724491-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>5.037,47</t>
+          <t>33,42</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>1726324</t>
+          <t>1724537</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -11306,24 +11306,24 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>BMD-1726324-HAGAP.pdf</t>
+          <t>BMD-1724537-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>245,31</t>
+          <t>2.386,57</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>1726496</t>
+          <t>1724551</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -11333,24 +11333,24 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>BMD-1726496-HAGAP.pdf</t>
+          <t>BMD-1724551-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>24.645,05</t>
+          <t>1.387,89</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>1726737</t>
+          <t>1725260</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -11360,24 +11360,24 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>BMD-1726737-HAGAP.pdf</t>
+          <t>BMD-1725260-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>4.070,08</t>
+          <t>10,16</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>1726890</t>
+          <t>1726320</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -11387,24 +11387,24 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>BMD-1726890-HAGAP.pdf</t>
+          <t>BMD-1726320-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>3.252,02</t>
+          <t>5.037,47</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>1727287</t>
+          <t>1726324</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -11414,12 +11414,12 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>BMD-1727287-HAGAP.pdf</t>
+          <t>BMD-1726324-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>489,21</t>
+          <t>245,31</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -11431,7 +11431,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>1727322</t>
+          <t>1726496</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -11441,24 +11441,24 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>BMD-1727322-HAGAP.pdf</t>
+          <t>BMD-1726496-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>148,16</t>
+          <t>24.645,05</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>1727335</t>
+          <t>1726541</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -11468,24 +11468,24 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>BMD-1727335-HAGAP.pdf</t>
+          <t>BMD-1726541-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>5.053,73</t>
+          <t>4.972,33</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>1727529</t>
+          <t>1726737</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -11495,24 +11495,24 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>BMD-1727529-HAGAP.pdf</t>
+          <t>BMD-1726737-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>4.366,81</t>
+          <t>4.070,08</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>1727808I</t>
+          <t>1726890</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -11522,24 +11522,24 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>BMD-1727808I-HAGAP.pdf</t>
+          <t>BMD-1726890-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>2.562,33</t>
+          <t>3.252,02</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>1727881</t>
+          <t>1727287</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -11549,24 +11549,24 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>BMD-1727881-HAGAP.pdf</t>
+          <t>BMD-1727287-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>2.707,35</t>
+          <t>489,21</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>1729786</t>
+          <t>1727322</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -11576,24 +11576,24 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>BMD-1729786-HAGAP.pdf</t>
+          <t>BMD-1727322-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>45.387,32</t>
+          <t>148,16</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>1729828</t>
+          <t>1727335</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -11603,24 +11603,24 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>BMD-1729828-HAGAP.pdf</t>
+          <t>BMD-1727335-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>914,81</t>
+          <t>5.053,73</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>1730222</t>
+          <t>1727529</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -11630,24 +11630,24 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>BMD-1730222-HAGAP.pdf</t>
+          <t>BMD-1727529-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>3.155,66</t>
+          <t>4.366,81</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>1730763</t>
+          <t>1727808I</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -11657,24 +11657,24 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>BMD-1730763-HAGAP.pdf</t>
+          <t>BMD-1727808I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>729,41</t>
+          <t>2.562,33</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>1730822</t>
+          <t>1727881</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -11684,24 +11684,24 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>BMD-1730822-HAGAP.pdf</t>
+          <t>BMD-1727881-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>512,56</t>
+          <t>2.707,35</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>1731653</t>
+          <t>1729553</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -11711,24 +11711,24 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>BMD-1731653-HAGAP.pdf</t>
+          <t>BMD-1729553-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>5.940,43</t>
+          <t>11.151,84</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>1733419I</t>
+          <t>1729786</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -11738,24 +11738,24 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>BMD-1733419I-HAGAP.pdf</t>
+          <t>BMD-1729786-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>1.171,48</t>
+          <t>45.387,32</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>1704074</t>
+          <t>1729828</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -11765,24 +11765,24 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>BMD.-1704074-HAGAP.pdf</t>
+          <t>BMD-1729828-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>17.644,40</t>
+          <t>914,81</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1730222</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -11792,24 +11792,24 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>BMD.-1713044C.-HAGAP.pdf</t>
+          <t>BMD-1730222-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>3.155,66</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1730763</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -11819,105 +11819,105 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>BMD.1715327-HAGAP.pdf</t>
+          <t>BMD-1730763-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>729,41</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1730822</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>BMDFINAL-1708877-HAGAP.pdf</t>
+          <t>BMD-1730822-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>512,56</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1731653</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>BMDFINAL-1712957-HAGAP.pdf</t>
+          <t>BMD-1731653-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>5.940,43</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1733419I</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>BMDFINAL-1717332-HAGAP.pdf</t>
+          <t>BMD-1733419I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.171,48</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1704074</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -11927,24 +11927,24 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
+          <t>BMD.-1704074-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>18.169,34</t>
+          <t>17.644,40</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -11954,24 +11954,24 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
+          <t>BMD.-1713044C.-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>6.951,82</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -11981,66 +11981,66 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
+          <t>BMD.1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>2.177,64</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
+          <t>BMDFINAL-1708877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>2.619,71</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
+          <t>BMDFINAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>954,64</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -12052,34 +12052,34 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
+          <t>BMDFINAL-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>4.418,94</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -12089,24 +12089,24 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>5.417,39</t>
+          <t>18.169,34</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -12116,24 +12116,24 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>2.744,71</t>
+          <t>6.951,82</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>913,84</t>
+          <t>2.177,64</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -12160,7 +12160,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -12170,12 +12170,12 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>1.675,57</t>
+          <t>2.619,71</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -12187,7 +12187,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -12197,24 +12197,24 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1724491-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>14.377,51</t>
+          <t>954,64</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>1692415</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -12224,24 +12224,24 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>BMD_1692415 - HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>4.712,56</t>
+          <t>4.418,94</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>1717315</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -12251,24 +12251,24 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>BMD_1717315_HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>13.183,29</t>
+          <t>5.417,39</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>1725869</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -12278,169 +12278,169 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>BMD_1725869_HAGAP.pdf</t>
+          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.744,71</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>FF0-1712766-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>913,84</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>1726737</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>FF0-1726737-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.675,57</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>FFO  -1719135-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1724491-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>14.377,51</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>1629477I</t>
+          <t>1692415</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>FFO -  1629477I - HAGAP.pdf</t>
+          <t>BMD_1692415 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>4.712,56</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>1510407</t>
+          <t>1717315</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>FFO - 1510407 - HAGAP - 20-07-2026.pdf</t>
+          <t>BMD_1717315_HAGAP.pdf</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.183,29</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>1658892</t>
+          <t>1725869</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>FFO - 1658892 - HAGAP - 15-07-2026.pdf</t>
+          <t>BMD_1725869_HAGAP.pdf</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -12450,14 +12450,14 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>1660062C</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>FFO - 1660062C - HAGAP.pdf</t>
+          <t>FF0-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -12477,14 +12477,14 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>1660062I</t>
+          <t>1726737</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>FFO - 1660062I - HAGAP.pdf</t>
+          <t>FF0-1726737-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -12504,14 +12504,14 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>FFO - 1677314 - HAGAP.pdf</t>
+          <t>FFO  -1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -12531,14 +12531,14 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1629477I</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>FFO - 1677316 HAGAP.pdf</t>
+          <t>FFO -  1629477I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -12558,14 +12558,14 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>1686607C</t>
+          <t>1510407</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -12575,7 +12575,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>FFO - 1686607C - HAGAP.pdf</t>
+          <t>FFO - 1510407 - HAGAP - 20-07-2026.pdf</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -12585,14 +12585,14 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>1686607I</t>
+          <t>1658892</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>FFO - 1686607I - HAGAP.pdf</t>
+          <t>FFO - 1658892 - HAGAP - 15-07-2026.pdf</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -12612,14 +12612,14 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1660062C</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>FFO - 1688115C - HAGAP.pdf</t>
+          <t>FFO - 1660062C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -12639,14 +12639,14 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1660062I</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -12656,7 +12656,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>FFO - 1688115I - HAGAP.pdf</t>
+          <t>FFO - 1660062I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -12666,14 +12666,14 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>1689264</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -12683,24 +12683,24 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>FFO - 1689264 - HAGAP.pdf</t>
+          <t>FFO - 1677314 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>2.288,38</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -12710,7 +12710,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>FFO - 1691534 - HAGAP - 03-07-2026.pdf</t>
+          <t>FFO - 1677316 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -12720,14 +12720,14 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>1692174</t>
+          <t>1686607C</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -12737,7 +12737,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>FFO - 1692174 - HAGAP.pdf</t>
+          <t>FFO - 1686607C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -12747,14 +12747,14 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>1694861</t>
+          <t>1686607I</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -12764,7 +12764,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>FFO - 1694861 - HAGAP.pdf</t>
+          <t>FFO - 1686607I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -12774,14 +12774,14 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>FFO - 1695716 - HAGAP.pdf</t>
+          <t>FFO - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -12801,14 +12801,14 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>1697210I</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -12818,7 +12818,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>FFO - 1697210I - HAGAP.pdf</t>
+          <t>FFO - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -12828,14 +12828,14 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>1698047</t>
+          <t>1689264</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -12845,24 +12845,24 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>FFO - 1698047 - HAGAP - 30-04-2026.pdf</t>
+          <t>FFO - 1689264 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.288,38</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>FFO - 1698056 - HAGAP - 17-07-2026.pdf</t>
+          <t>FFO - 1691534 - HAGAP - 03-07-2026.pdf</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -12882,14 +12882,14 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>1702127</t>
+          <t>1692174</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>FFO - 1702127 - HAGAP.pdf</t>
+          <t>FFO - 1692174 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -12909,14 +12909,14 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>1702640</t>
+          <t>1694861</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>FFO - 1702640 - HAGAP - 10-07-2026.pdf</t>
+          <t>FFO - 1694861 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -12936,14 +12936,14 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -12953,7 +12953,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>FFO - 1702776C - HAGAP.pdf</t>
+          <t>FFO - 1695716 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -12963,14 +12963,14 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1697210I</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -12980,7 +12980,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>FFO - 1702776I - HAGAP.pdf</t>
+          <t>FFO - 1697210I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -12990,14 +12990,14 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>1704802</t>
+          <t>1698047</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -13007,7 +13007,7 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>FFO - 1704802 - HAGAP - 31-07-2026.pdf</t>
+          <t>FFO - 1698047 - HAGAP - 30-04-2026.pdf</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -13017,14 +13017,14 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>FFO - 1704867 - ASP.pdf</t>
+          <t>FFO - 1698056 - HAGAP - 17-07-2026.pdf</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -13044,14 +13044,14 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>1705802I</t>
+          <t>1702127</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>FFO - 1705802I - HAGAP.pdf</t>
+          <t>FFO - 1702127 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -13071,14 +13071,14 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>1707174</t>
+          <t>1702640</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>FFO - 1707174 - HAGAP - 17-07-2026.pdf</t>
+          <t>FFO - 1702640 - HAGAP - 10-07-2026.pdf</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -13098,14 +13098,14 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>1708906</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>FFO - 1708906 - HAGAP.pdf</t>
+          <t>FFO - 1702776C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -13125,14 +13125,14 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>1709419</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -13142,7 +13142,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>FFO - 1709419 - HAGAP.pdf</t>
+          <t>FFO - 1702776I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -13152,14 +13152,14 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>1709995</t>
+          <t>1704802</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -13169,7 +13169,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>FFO - 1709995 - HAGAP.pdf</t>
+          <t>FFO - 1704802 - HAGAP - 31-07-2026.pdf</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -13179,14 +13179,14 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>1710287I</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>FFO - 1710287I - HAGAP - 06-08-2026.pdf</t>
+          <t>FFO - 1704867 - ASP.pdf</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -13206,14 +13206,14 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>1710332</t>
+          <t>1705802I</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>FFO - 1710332 - HAGAP.pdf</t>
+          <t>FFO - 1705802I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -13233,14 +13233,14 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1707174</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>FFO - 1710735 HAGAP.pdf</t>
+          <t>FFO - 1707174 - HAGAP - 17-07-2026.pdf</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -13260,14 +13260,14 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1708906</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>FFO - 1711384 - HAGAP.pdf</t>
+          <t>FFO - 1708906 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -13287,14 +13287,14 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>1711454</t>
+          <t>1709419</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>FFO - 1711454 HAGAP.pdf</t>
+          <t>FFO - 1709419 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -13314,14 +13314,14 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>1711489</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>FFO - 1711489 - HAGAP.pdf</t>
+          <t>FFO - 1709995 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -13341,14 +13341,14 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1710287I</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -13358,7 +13358,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>FFO - 1712538 - HAGAP.pdf</t>
+          <t>FFO - 1710287I - HAGAP - 06-08-2026.pdf</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -13368,14 +13368,14 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1710332</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -13385,7 +13385,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>FFO - 1713221 - HAGAP.pdf</t>
+          <t>FFO - 1710332 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -13395,14 +13395,14 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>1713223</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -13412,7 +13412,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>FFO - 1713223 - HAGAP - 13-08-2026.pdf</t>
+          <t>FFO - 1710735 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -13422,14 +13422,14 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -13439,7 +13439,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
+          <t>FFO - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -13449,14 +13449,14 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>1713260</t>
+          <t>1711454</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>FFO - 1713260 - HAGAP.pdf</t>
+          <t>FFO - 1711454 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -13476,14 +13476,14 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1711489</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -13493,24 +13493,24 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>FFO - 1715278 - HAGAP.pdf</t>
+          <t>FFO - 1711489 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>306,36</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>FFO - 1715688 - HAGAP.pdf</t>
+          <t>FFO - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -13530,14 +13530,14 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -13547,7 +13547,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
+          <t>FFO - 1713221 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -13557,14 +13557,14 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>1718954</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>FFO - 1718954 - HAGAP - 29-07-2026.pdf</t>
+          <t>FFO - 1713223 - HAGAP - 13-08-2026.pdf</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -13584,14 +13584,14 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>1718958</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>FFO - 1718958 - HAGAP - 31-07-2026 1.pdf</t>
+          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -13611,14 +13611,14 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>1719488</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>FFO - 1719488 - HAGAP - 10-09-2026.pdf</t>
+          <t>FFO - 1713260 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -13638,14 +13638,14 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>1719775</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -13655,24 +13655,24 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>FFO - 1719775 - HAGAP - 30-07-2026.pdf</t>
+          <t>FFO - 1715278 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>306,36</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>1720914</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -13682,7 +13682,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>FFO - 1720914 - HAGAP.pdf</t>
+          <t>FFO - 1715688 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -13692,14 +13692,14 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>1721180</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -13709,7 +13709,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>FFO - 1721180 - HAGAP - 20-08-2026.pdf</t>
+          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -13719,14 +13719,14 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>1721886</t>
+          <t>1718954</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>FFO - 1721886 - HAGAP.pdf</t>
+          <t>FFO - 1718954 - HAGAP - 29-07-2026.pdf</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -13746,14 +13746,14 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>1722321</t>
+          <t>1718958</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>FFO - 1722321 - HAGAP - 15-07-2026.pdf</t>
+          <t>FFO - 1718958 - HAGAP - 31-07-2026 1.pdf</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -13773,14 +13773,14 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>1722779</t>
+          <t>1719488</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>FFO - 1722779 - HAGAP.pdf</t>
+          <t>FFO - 1719488 - HAGAP - 10-09-2026.pdf</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -13800,14 +13800,14 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>1722803</t>
+          <t>1719775</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -13817,7 +13817,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>FFO - 1722803 - HAGAP - 31-07-2026.pdf</t>
+          <t>FFO - 1719775 - HAGAP - 30-07-2026.pdf</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
@@ -13827,14 +13827,14 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>1722905</t>
+          <t>1720914</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -13844,7 +13844,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>FFO - 1722905 - HAGAP - 21-08-2026.pdf</t>
+          <t>FFO - 1720914 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -13854,14 +13854,14 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>1722924</t>
+          <t>1721180</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -13871,7 +13871,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>FFO - 1722924 - HAGAP - 17-08-2026.pdf</t>
+          <t>FFO - 1721180 - HAGAP - 20-08-2026.pdf</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
@@ -13881,14 +13881,14 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>1723724</t>
+          <t>1721886</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -13898,7 +13898,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>FFO - 1723724 - HAGAP - 26-08-2026.pdf</t>
+          <t>FFO - 1721886 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -13908,14 +13908,14 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>1723727</t>
+          <t>1722321</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -13925,7 +13925,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>FFO - 1723727 - HAGAP - 26-08-2026.pdf</t>
+          <t>FFO - 1722321 - HAGAP - 15-07-2026.pdf</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -13935,14 +13935,14 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>1724051I</t>
+          <t>1722779</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>FFO - 1724051I - HAGAP - 15-07-2026.pdf</t>
+          <t>FFO - 1722779 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
@@ -13962,14 +13962,14 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>1724680</t>
+          <t>1722803</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -13979,7 +13979,7 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>FFO - 1724680 - HAGAP.pdf</t>
+          <t>FFO - 1722803 - HAGAP - 31-07-2026.pdf</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -13989,14 +13989,14 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>1725738C</t>
+          <t>1722905</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -14006,7 +14006,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>FFO - 1725738C - HAGAP (2).pdf</t>
+          <t>FFO - 1722905 - HAGAP - 21-08-2026.pdf</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -14016,14 +14016,14 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>1725738I</t>
+          <t>1722924</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -14033,7 +14033,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>FFO - 1725738I - HAGAP.pdf</t>
+          <t>FFO - 1722924 - HAGAP - 17-08-2026.pdf</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -14043,14 +14043,14 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>1726388</t>
+          <t>1723724</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -14060,7 +14060,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>FFO - 1726388 - HAGAP - 21-08-2026.pdf</t>
+          <t>FFO - 1723724 - HAGAP - 26-08-2026.pdf</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -14070,14 +14070,14 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>1727778</t>
+          <t>1723727</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -14087,7 +14087,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>FFO - 1727778 - HAGAP.pdf</t>
+          <t>FFO - 1723727 - HAGAP - 26-08-2026.pdf</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
@@ -14097,14 +14097,14 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>1727882</t>
+          <t>1724051I</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -14114,7 +14114,7 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>FFO - 1727882 - HAGAP - 27-08-2026.pdf</t>
+          <t>FFO - 1724051I - HAGAP - 15-07-2026.pdf</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -14124,14 +14124,14 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>1729300</t>
+          <t>1724680</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>FFO - 1729300 - HAGAP - 21-08-2026.pdf</t>
+          <t>FFO - 1724680 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -14151,14 +14151,14 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>1729668</t>
+          <t>1725738C</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -14168,7 +14168,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>FFO - 1729668 - HAGAP - 31-07-2026.pdf</t>
+          <t>FFO - 1725738C - HAGAP (2).pdf</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -14178,14 +14178,14 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>1730270</t>
+          <t>1725738I</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>FFO - 1730270 - HAGAP - 31-07-2026.pdf</t>
+          <t>FFO - 1725738I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -14212,7 +14212,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>1730642I</t>
+          <t>1726388</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -14222,7 +14222,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>FFO - 1730642I - HAGAP - 14-08-2026.pdf</t>
+          <t>FFO - 1726388 - HAGAP - 21-08-2026.pdf</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -14232,14 +14232,14 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>1730707</t>
+          <t>1727778</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>FFO - 1730707 - HAGAP - 26-08-2026.pdf</t>
+          <t>FFO - 1727778 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -14259,14 +14259,14 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>1731746</t>
+          <t>1727882</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>FFO - 1731746 - HAGAP - 27-08-2026.pdf</t>
+          <t>FFO - 1727882 - HAGAP - 27-08-2026.pdf</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -14293,7 +14293,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>1520615</t>
+          <t>1729300</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -14303,7 +14303,7 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>FFO 1520615 HAGAP.pdf</t>
+          <t>FFO - 1729300 - HAGAP - 21-08-2026.pdf</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
@@ -14313,14 +14313,14 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>1641139I</t>
+          <t>1729668</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>FFO 1641139I HAGAP.pdf</t>
+          <t>FFO - 1729668 - HAGAP - 31-07-2026.pdf</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -14340,14 +14340,14 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>1682195</t>
+          <t>1730270</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>FFO 1682195 HAGAP.pdf</t>
+          <t>FFO - 1730270 - HAGAP - 31-07-2026.pdf</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
@@ -14367,14 +14367,14 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>1693027</t>
+          <t>1730642I</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -14384,7 +14384,7 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>FFO 1693027 HAGAP.pdf</t>
+          <t>FFO - 1730642I - HAGAP - 14-08-2026.pdf</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
@@ -14394,14 +14394,14 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1730707</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -14411,7 +14411,7 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>FFO 1699516 HAGAP.pdf</t>
+          <t>FFO - 1730707 - HAGAP - 26-08-2026.pdf</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -14421,14 +14421,14 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1731746</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -14438,7 +14438,7 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>FFO 1704525 HAGAP.pdf</t>
+          <t>FFO - 1731746 - HAGAP - 27-08-2026.pdf</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -14448,14 +14448,14 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>1710329</t>
+          <t>1520615</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -14465,7 +14465,7 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>FFO 1710329 HAGAP.pdf</t>
+          <t>FFO 1520615 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
@@ -14475,14 +14475,14 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>1710736</t>
+          <t>1641139I</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>FFO 1710736 HAGAP.pdf</t>
+          <t>FFO 1641139I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -14502,14 +14502,14 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>1710975</t>
+          <t>1682195</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>FFO 1710975 HAGAP.pdf</t>
+          <t>FFO 1682195 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
@@ -14529,14 +14529,14 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1693027</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>FFO 1711525 HAGAP.pdf</t>
+          <t>FFO 1693027 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
@@ -14556,14 +14556,14 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>FFO 1712533 HAGAP.pdf</t>
+          <t>FFO 1699516 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -14583,14 +14583,14 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>1713045</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -14600,7 +14600,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>FFO 1713045 HAGAP.pdf</t>
+          <t>FFO 1704525 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
@@ -14610,14 +14610,14 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>1713351</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -14627,7 +14627,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>FFO 1713351 HAGAP.pdf</t>
+          <t>FFO 1710329 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
@@ -14637,14 +14637,14 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>1713435I</t>
+          <t>1710736</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -14654,7 +14654,7 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>FFO 1713435I HAGAP.pdf</t>
+          <t>FFO 1710736 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
@@ -14671,7 +14671,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1710975</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -14681,7 +14681,7 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>FFO 1713679 HAGAP.pdf</t>
+          <t>FFO 1710975 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
@@ -14691,14 +14691,14 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>1714364</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -14708,7 +14708,7 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>FFO 1714364 HAGAP.pdf</t>
+          <t>FFO 1711525 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
@@ -14718,14 +14718,14 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -14735,7 +14735,7 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>FFO 1714729 HAGAP.pdf</t>
+          <t>FFO 1712533 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -14745,14 +14745,14 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>1715154</t>
+          <t>1713045</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>FFO 1715154 HAGAP.pdf</t>
+          <t>FFO 1713045 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
@@ -14772,14 +14772,14 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1713351</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -14789,24 +14789,24 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>FFO 1718561 HAGAP.pdf</t>
+          <t>FFO 1713351 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>1.543,28</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1713435I</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>FFO 1718803 HAGAP.pdf</t>
+          <t>FFO 1713435I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -14826,14 +14826,14 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -14843,7 +14843,7 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>FFO 1719097 HAGAP.pdf</t>
+          <t>FFO 1713679 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
@@ -14853,14 +14853,14 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1714364</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -14870,7 +14870,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>FFO 1719155 HAGAP.pdf</t>
+          <t>FFO 1714364 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -14880,14 +14880,14 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -14897,7 +14897,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>FFO 1719213 HAGAP.pdf</t>
+          <t>FFO 1714729 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -14907,14 +14907,14 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1715154</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>FFO 1720721 HAGAP.pdf</t>
+          <t>FFO 1715154 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -14934,14 +14934,14 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>1720909</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -14951,24 +14951,24 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>FFO 1720909 HAGAP.pdf</t>
+          <t>FFO 1718561 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.543,28</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>FFO 1720920 HAGAP.pdf</t>
+          <t>FFO 1718803 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -14988,14 +14988,14 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>1721595</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -15005,7 +15005,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>FFO 1721595 HAGAP.pdf</t>
+          <t>FFO 1719097 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -15015,14 +15015,14 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>1722320</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -15032,7 +15032,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>FFO 1722320 HAGAP.pdf</t>
+          <t>FFO 1719155 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -15042,14 +15042,14 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>1722904</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -15059,7 +15059,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>FFO 1722904 HAGAP.pdf</t>
+          <t>FFO 1719213 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
@@ -15069,14 +15069,14 @@
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>1723722</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>FFO 1723722 HAGAP.pdf</t>
+          <t>FFO 1720721 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
@@ -15096,14 +15096,14 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>1724053</t>
+          <t>1720909</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -15113,7 +15113,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>FFO 1724053 HAGAP.pdf</t>
+          <t>FFO 1720909 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
@@ -15123,14 +15123,14 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>1724663</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -15140,24 +15140,24 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>FFO 1724663 HAGAP.pdf</t>
+          <t>FFO 1720920 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>3.091,28</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>1728642</t>
+          <t>1721595</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -15167,7 +15167,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>FFO 1728642 HAGAP -.pdf</t>
+          <t>FFO 1721595 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
@@ -15177,14 +15177,14 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>1730908</t>
+          <t>1722320</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -15194,7 +15194,7 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>FFO 1730908 HAGAP.pdf</t>
+          <t>FFO 1722320 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
@@ -15204,14 +15204,14 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1722904</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>FFO-1667141-HAGAP.pdf</t>
+          <t>FFO 1722904 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
@@ -15231,14 +15231,14 @@
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>1674093</t>
+          <t>1723722</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -15248,7 +15248,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>FFO-1674093-HAGAP.pdf</t>
+          <t>FFO 1723722 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
@@ -15258,14 +15258,14 @@
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1724053</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -15275,7 +15275,7 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>FFO-1675389-HAGAP.pdf</t>
+          <t>FFO 1724053 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
@@ -15285,14 +15285,14 @@
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>1676605</t>
+          <t>1724663</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -15302,24 +15302,24 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>FFO-1676605-HAGAP.pdf</t>
+          <t>FFO 1724663 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.091,28</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>1691390</t>
+          <t>1728642</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -15329,7 +15329,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>FFO-1691390-HAGAP.pdf</t>
+          <t>FFO 1728642 HAGAP -.pdf</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
@@ -15339,14 +15339,14 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1730908</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -15356,7 +15356,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>FFO-1694841-HAGAP.pdf</t>
+          <t>FFO 1730908 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
@@ -15366,14 +15366,14 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -15383,7 +15383,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>FFO-1703223-HAGAP.pdf</t>
+          <t>FFO-1667141-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
@@ -15393,14 +15393,14 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>1704074</t>
+          <t>1671216C</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -15410,7 +15410,7 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>FFO-1704074-HAGAP.pdf</t>
+          <t>FFO-1671216C-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
@@ -15420,14 +15420,14 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1671216I</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>FFO-1704877-HAGAP.pdf</t>
+          <t>FFO-1671216I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
@@ -15447,14 +15447,14 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>1704953</t>
+          <t>1674093</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>FFO-1704953-HAGAP.pdf</t>
+          <t>FFO-1674093-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -15474,14 +15474,14 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -15491,7 +15491,7 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>FFO-1708877-HAGAP.pdf</t>
+          <t>FFO-1675389-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
@@ -15501,14 +15501,14 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>1708908</t>
+          <t>1676605</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -15518,24 +15518,24 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>FFO-1708908-HAGAP.pdf</t>
+          <t>FFO-1676605-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>3.563,85</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1691390</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -15545,7 +15545,7 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>FFO-1709486-HAGAP.pdf</t>
+          <t>FFO-1691390-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
@@ -15555,14 +15555,14 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>FFO-1710116-HAGAP.pdf</t>
+          <t>FFO-1694841-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
@@ -15582,14 +15582,14 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>1710287C</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>FFO-1710287C-HAGAP.pdf</t>
+          <t>FFO-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
@@ -15609,14 +15609,14 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>1711110</t>
+          <t>1704074</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -15626,7 +15626,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>FFO-1711110-HAGAP.pdf</t>
+          <t>FFO-1704074-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
@@ -15636,14 +15636,14 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>1711507</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -15653,7 +15653,7 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>FFO-1711507-HAGAP.pdf</t>
+          <t>FFO-1704877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
@@ -15663,14 +15663,14 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1704953</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>FFO-1711775-HAGAP.pdf</t>
+          <t>FFO-1704953-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
@@ -15690,14 +15690,14 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>1711788</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -15707,7 +15707,7 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>FFO-1711788-HAGAP.pdf</t>
+          <t>FFO-1708877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
@@ -15717,14 +15717,14 @@
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1708908</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -15734,24 +15734,24 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>FFO-1712530=-HAGAP.pdf</t>
+          <t>FFO-1708908-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.563,85</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -15761,7 +15761,7 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>FFO-1712531-HAGAP.pdf</t>
+          <t>FFO-1709486-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
@@ -15771,14 +15771,14 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>FFO-1712547-HAGAP.pdf</t>
+          <t>FFO-1710116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
@@ -15798,14 +15798,14 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1710287C</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -15815,7 +15815,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>FFO-1712550-HAGAP.pdf</t>
+          <t>FFO-1710287C-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
@@ -15825,14 +15825,14 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1711110</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -15842,7 +15842,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>FFO-1713044C.-HAGAP.pdf</t>
+          <t>FFO-1711110-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
@@ -15852,14 +15852,14 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -15869,7 +15869,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>FFO-1713044II-HAGAP.pdf</t>
+          <t>FFO-1711507-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
@@ -15879,14 +15879,14 @@
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -15896,7 +15896,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>FFO-1713226-HAGAP.pdf</t>
+          <t>FFO-1711775-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -15906,14 +15906,14 @@
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1711788</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>FFO-1713262-HAGAP.pdf</t>
+          <t>FFO-1711788-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
@@ -15933,14 +15933,14 @@
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>1713626</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>FFO-1713626-HAGAP.pdf</t>
+          <t>FFO-1712530=-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
@@ -15960,14 +15960,14 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>1713656I</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>FFO-1713656I-HAGAP.pdf</t>
+          <t>FFO-1712531-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
@@ -15987,14 +15987,14 @@
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>1713681</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -16004,7 +16004,7 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>FFO-1713681-HAGAP.pdf</t>
+          <t>FFO-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
@@ -16014,14 +16014,14 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>1713903C</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -16031,7 +16031,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>FFO-1713903C-HAGAP.pdf</t>
+          <t>FFO-1712550-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
@@ -16041,14 +16041,14 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>1713903I</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -16058,7 +16058,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>FFO-1713903I-HAGAP.pdf</t>
+          <t>FFO-1713044C.-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
@@ -16068,14 +16068,14 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -16085,7 +16085,7 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>FFO-1714342-HAGAP.pdf</t>
+          <t>FFO-1713044II-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
@@ -16095,14 +16095,14 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>1714348</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -16112,7 +16112,7 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>FFO-1714348-HAGAP.pdf</t>
+          <t>FFO-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
@@ -16122,14 +16122,14 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>1714699</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -16139,7 +16139,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>FFO-1714699-HAGAP.pdf</t>
+          <t>FFO-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
@@ -16149,14 +16149,14 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>1714857</t>
+          <t>1713626</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>FFO-1714857-HAGAP.pdf</t>
+          <t>FFO-1713626-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
@@ -16183,7 +16183,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713656I</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -16193,7 +16193,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>FFO-1714909-HAGAP.pdf</t>
+          <t>FFO-1713656I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
@@ -16203,14 +16203,14 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1713681</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -16220,7 +16220,7 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>FFO-1715127-HAGAP.pdf</t>
+          <t>FFO-1713681-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
@@ -16230,14 +16230,14 @@
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1713903C</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>FFO-1715201-HAGAP.pdf</t>
+          <t>FFO-1713903C-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
@@ -16257,14 +16257,14 @@
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1713903I</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>FFO-1715257I-HAGAP.pdf</t>
+          <t>FFO-1713903I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
@@ -16284,14 +16284,14 @@
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1713916</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -16301,24 +16301,24 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>FFO-1715327-HAGAP.pdf</t>
+          <t>FFO-1713916-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>65,98</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>FFO-1715668-HAGAP.pdf</t>
+          <t>FFO-1714342-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
@@ -16338,14 +16338,14 @@
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>1715710</t>
+          <t>1714348</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -16355,7 +16355,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>FFO-1715710-HAGAP.pdf</t>
+          <t>FFO-1714348-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
@@ -16365,14 +16365,14 @@
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>1715955I</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -16382,7 +16382,7 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>FFO-1715955I-HAGAP.pdf</t>
+          <t>FFO-1714699-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -16392,14 +16392,14 @@
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1714857</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -16409,24 +16409,24 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>FFO-1717168-HAGAP.pdf</t>
+          <t>FFO-1714857-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>87,00</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -16436,24 +16436,24 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>FFO-1717332-HAGAP.pdf</t>
+          <t>FFO-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>176,23</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>1718019</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -16463,7 +16463,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>FFO-1718019-HAGAP.pdf</t>
+          <t>FFO-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
@@ -16473,14 +16473,14 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>1718555</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -16490,7 +16490,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>FFO-1718555-HAGAP.pdf</t>
+          <t>FFO-1715201-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
@@ -16500,14 +16500,14 @@
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>1718951</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -16517,7 +16517,7 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>FFO-1718951-HAGAP.pdf</t>
+          <t>FFO-1715257I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
@@ -16527,14 +16527,14 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -16544,24 +16544,24 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>FFO-1719070-HAGAP.pdf</t>
+          <t>FFO-1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>65,98</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>1719077</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -16571,7 +16571,7 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>FFO-1719077-HAGAP.pdf</t>
+          <t>FFO-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
@@ -16581,14 +16581,14 @@
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>1719154</t>
+          <t>1715710</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>FFO-1719154-HAGAP.pdf</t>
+          <t>FFO-1715710-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
@@ -16608,14 +16608,14 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -16625,7 +16625,7 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>FFO-1719881-HAGAP.pdf</t>
+          <t>FFO-1715955I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
@@ -16635,14 +16635,14 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -16652,24 +16652,24 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>FFO-1721869-HAGAP.pdf</t>
+          <t>FFO-1717168-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>87,00</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -16679,24 +16679,24 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>FFO-1724491-HAGAP.pdf</t>
+          <t>FFO-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>176,23</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>1724537</t>
+          <t>1718019</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -16706,7 +16706,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>FFO-1724537-HAGAP.pdf</t>
+          <t>FFO-1718019-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
@@ -16716,14 +16716,14 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>1724551</t>
+          <t>1718555</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -16733,7 +16733,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>FFO-1724551-HAGAP.pdf</t>
+          <t>FFO-1718555-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
@@ -16743,14 +16743,14 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1718951</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -16760,7 +16760,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>FFO-1725260-HAGAP.pdf</t>
+          <t>FFO-1718951-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
@@ -16770,14 +16770,14 @@
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>1726320</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -16787,7 +16787,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>FFO-1726320-HAGAP.pdf</t>
+          <t>FFO-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
@@ -16797,14 +16797,14 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>1726324</t>
+          <t>1719077</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>FFO-1726324-HAGAP.pdf</t>
+          <t>FFO-1719077-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
@@ -16824,14 +16824,14 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>1726496</t>
+          <t>1719154</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>FFO-1726496-HAGAP.pdf</t>
+          <t>FFO-1719154-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
@@ -16851,14 +16851,14 @@
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>1726890</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>FFO-1726890-HAGAP.pdf</t>
+          <t>FFO-1719881-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -16878,14 +16878,14 @@
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>1727187</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -16895,7 +16895,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>FFO-1727187-HAGAP.pdf</t>
+          <t>FFO-1721869-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -16905,14 +16905,14 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>1727322</t>
+          <t>1723726</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -16922,7 +16922,7 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>FFO-1727322-HAGAP.pdf</t>
+          <t>FFO-1723726-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
@@ -16932,14 +16932,14 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>1727335</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -16949,7 +16949,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>FFO-1727335-HAGAP.pdf</t>
+          <t>FFO-1724491-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
@@ -16966,7 +16966,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>1727529</t>
+          <t>1724537</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -16976,7 +16976,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>FFO-1727529-HAGAP.pdf</t>
+          <t>FFO-1724537-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
@@ -16986,14 +16986,14 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>1727808</t>
+          <t>1724551</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -17003,7 +17003,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>FFO-1727808-HAGAP.pdf</t>
+          <t>FFO-1724551-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -17013,14 +17013,14 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>1727881</t>
+          <t>1725260</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -17030,7 +17030,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>FFO-1727881-HAGAP.pdf</t>
+          <t>FFO-1725260-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
@@ -17040,14 +17040,14 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>1729786</t>
+          <t>1726320</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -17057,7 +17057,7 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>FFO-1729786-HAGAP.pdf</t>
+          <t>FFO-1726320-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
@@ -17067,14 +17067,14 @@
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>1729828</t>
+          <t>1726324</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -17084,7 +17084,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>FFO-1729828-HAGAP.pdf</t>
+          <t>FFO-1726324-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
@@ -17094,14 +17094,14 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>1730222</t>
+          <t>1726496</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -17111,7 +17111,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>FFO-1730222-HAGAP.pdf</t>
+          <t>FFO-1726496-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -17128,7 +17128,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>1730763</t>
+          <t>1726541</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -17138,7 +17138,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>FFO-1730763-HAGAP.pdf</t>
+          <t>FFO-1726541-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
@@ -17148,14 +17148,14 @@
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>1730822</t>
+          <t>1726890</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -17165,7 +17165,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>FFO-1730822-HAGAP.pdf</t>
+          <t>FFO-1726890-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -17175,14 +17175,14 @@
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>1731653</t>
+          <t>1727187</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -17192,7 +17192,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>FFO-1731653-HAGAP.pdf</t>
+          <t>FFO-1727187-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
@@ -17202,14 +17202,14 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>1733419I</t>
+          <t>1727322</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>FFO-1733419I-HAGAP.pdf</t>
+          <t>FFO-1727322-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
@@ -17229,14 +17229,14 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1727335</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -17246,7 +17246,7 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>FFO.-1708066-HAGAP.pdf</t>
+          <t>FFO-1727335-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
@@ -17256,14 +17256,14 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1727529</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -17273,7 +17273,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>FFO.-1712957-HAGAP.pdf</t>
+          <t>FFO-1727529-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
@@ -17283,14 +17283,14 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>1713660</t>
+          <t>1727808</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -17300,7 +17300,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>FFO.-1713660-HAGAP.pdf</t>
+          <t>FFO-1727808-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
@@ -17310,14 +17310,14 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>1691380</t>
+          <t>1727881</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -17327,7 +17327,7 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>FFO_1691380.pdf</t>
+          <t>FFO-1727881-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
@@ -17337,14 +17337,14 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>1692415</t>
+          <t>1729553</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -17354,7 +17354,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>FFO_1692415 - HAGAP.pdf</t>
+          <t>FFO-1729553-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
@@ -17364,14 +17364,14 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>1717315</t>
+          <t>1729786</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -17381,7 +17381,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>FFO_1717315_HAGAP.pdf</t>
+          <t>FFO-1729786-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
@@ -17391,14 +17391,14 @@
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>1725869</t>
+          <t>1729828</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -17408,24 +17408,24 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>FFO_1725869_HAGAP.pdf</t>
+          <t>FFO-1729828-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>2.488,83</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1730222</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -17435,7 +17435,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>FFO´1718442-HAGAP.pdf</t>
+          <t>FFO-1730222-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
@@ -17445,24 +17445,24 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>1726320</t>
+          <t>1730763</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>MULLTA-1726320-HAGAP.pdf</t>
+          <t>FFO-1730763-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
@@ -17470,22 +17470,26 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E632" t="inlineStr"/>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1730822</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>MULT1712530-HAGAP.pdf</t>
+          <t>FFO-1730822-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
@@ -17493,22 +17497,26 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E633" t="inlineStr"/>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>1705034</t>
+          <t>1731653</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>MULTA - 1705034 - HAGAP.pdf</t>
+          <t>FFO-1731653-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
@@ -17516,22 +17524,26 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E634" t="inlineStr"/>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>1713223</t>
+          <t>1733419I</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>MULTA - 1713223 - HAGAP - 11-08-2026.pdf</t>
+          <t>FFO-1733419I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
@@ -17539,22 +17551,26 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E635" t="inlineStr"/>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>1719775</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>MULTA - 1719775 - HAGAP - 27-07-2026.pdf</t>
+          <t>FFO.-1708066-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
@@ -17562,22 +17578,26 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E636" t="inlineStr"/>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>1726388</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>MULTA - 1726388 - HAGAP - 20-08-2026.pdf</t>
+          <t>FFO.-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
@@ -17585,22 +17605,26 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E637" t="inlineStr"/>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>1729300</t>
+          <t>1713660</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>MULTA - 1729300 - HAGAP - 20-08-2026.pdf</t>
+          <t>FFO.-1713660-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
@@ -17608,22 +17632,26 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E638" t="inlineStr"/>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1691380</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>MULTA-1694841-HAGAP.pdf</t>
+          <t>FFO_1691380.pdf</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
@@ -17631,22 +17659,26 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E639" t="inlineStr"/>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1692415</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>MULTA-1703223-HAGAP.pdf</t>
+          <t>FFO_1692415 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
@@ -17654,22 +17686,26 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E640" t="inlineStr"/>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1717315</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>MULTA-1704877-HAGAP.pdf</t>
+          <t>FFO_1717315_HAGAP.pdf</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
@@ -17677,45 +17713,53 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E641" t="inlineStr"/>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>1711507</t>
+          <t>1725869</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>MULTA-1711507-HAGAP.pdf</t>
+          <t>FFO_1725869_HAGAP.pdf</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="E642" t="inlineStr"/>
+          <t>2.488,83</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>MULTA-1713044I-HAGAP.pdf</t>
+          <t>FFO´1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
@@ -17723,12 +17767,16 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E643" t="inlineStr"/>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>1713903I</t>
+          <t>1726320</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -17738,7 +17786,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>MULTA-1713903I-HAGAP.pdf</t>
+          <t>MULLTA-1726320-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
@@ -17751,7 +17799,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -17761,7 +17809,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>MULTA-1715327-HAGAP.pdf</t>
+          <t>MULT1712530-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
@@ -17774,7 +17822,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1705034</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -17784,7 +17832,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>MULTA-1724491-HAGAP.pdf</t>
+          <t>MULTA - 1705034 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
@@ -17797,7 +17845,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>1724537</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -17807,7 +17855,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>MULTA-1724537-HAGAP.pdf</t>
+          <t>MULTA - 1713223 - HAGAP - 11-08-2026.pdf</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
@@ -17820,7 +17868,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>1726890</t>
+          <t>1719775</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -17830,7 +17878,7 @@
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>MULTA-1726890-HAGAP.pdf</t>
+          <t>MULTA - 1719775 - HAGAP - 27-07-2026.pdf</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
@@ -17843,7 +17891,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>1727529</t>
+          <t>1726388</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -17853,7 +17901,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>MULTA-1727529-HAGAP.pdf</t>
+          <t>MULTA - 1726388 - HAGAP - 20-08-2026.pdf</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
@@ -17866,7 +17914,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>1729786</t>
+          <t>1729300</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -17876,7 +17924,7 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>MULTA-1729786-HAGAP.pdf</t>
+          <t>MULTA - 1729300 - HAGAP - 20-08-2026.pdf</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
@@ -17889,7 +17937,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>1730822</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -17899,7 +17947,7 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>MULTA-1730822-HAGAP.pdf</t>
+          <t>MULTA-1694841-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
@@ -17912,7 +17960,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>1730313</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
@@ -17922,24 +17970,20 @@
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>bmd 1730313.pdf</t>
+          <t>MULTA-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>2.885,97</t>
-        </is>
-      </c>
-      <c r="E652" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>1737272</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -17949,24 +17993,20 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>bmd 1737272.pdf</t>
+          <t>MULTA-1704877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>4.617,63</t>
-        </is>
-      </c>
-      <c r="E653" t="inlineStr">
-        <is>
-          <t>28/08/2026</t>
-        </is>
-      </c>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>1737274</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -17976,24 +18016,20 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>bmd 1737274.pdf</t>
+          <t>MULTA-1711507-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>4.617,63</t>
-        </is>
-      </c>
-      <c r="E654" t="inlineStr">
-        <is>
-          <t>28/08/2026</t>
-        </is>
-      </c>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr"/>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>1737280</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -18003,24 +18039,20 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>bmd 1737280.pdf</t>
+          <t>MULTA-1713044I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>2.886,03</t>
-        </is>
-      </c>
-      <c r="E655" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>1737483</t>
+          <t>1713903I</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -18030,24 +18062,20 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>bmd 1737483.pdf</t>
+          <t>MULTA-1713903I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>5.194,82</t>
-        </is>
-      </c>
-      <c r="E656" t="inlineStr">
-        <is>
-          <t>28/08/2026</t>
-        </is>
-      </c>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr"/>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>1737484</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -18057,24 +18085,20 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>bmd 1737484.pdf</t>
+          <t>MULTA-1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>5.194,82</t>
-        </is>
-      </c>
-      <c r="E657" t="inlineStr">
-        <is>
-          <t>28/08/2026</t>
-        </is>
-      </c>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr"/>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>1740643</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -18084,24 +18108,20 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>bmd 1740643.pdf</t>
+          <t>MULTA-1724491-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>4.617,63</t>
-        </is>
-      </c>
-      <c r="E658" t="inlineStr">
-        <is>
-          <t>28/08/2026</t>
-        </is>
-      </c>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr"/>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>1741124</t>
+          <t>1724537</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -18111,24 +18131,20 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>bmd 1741124.pdf</t>
+          <t>MULTA-1724537-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>2.885,97</t>
-        </is>
-      </c>
-      <c r="E659" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>1741248</t>
+          <t>1726890</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -18138,42 +18154,350 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>bmd 1741248.pdf</t>
+          <t>MULTA-1726890-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>4.617,63</t>
-        </is>
-      </c>
-      <c r="E660" t="inlineStr">
-        <is>
-          <t>28/08/2026</t>
-        </is>
-      </c>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr"/>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
+          <t>1727529</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>MULTA-1727529-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr"/>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>1729786</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>MULTA-1729786-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr"/>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>1730822</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>MULTA-1730822-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr"/>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>1730313</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>bmd 1730313.pdf</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>2.885,97</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>1737272</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>bmd 1737272.pdf</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>4.617,63</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>1737274</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>bmd 1737274.pdf</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>4.617,63</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>1737280</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>bmd 1737280.pdf</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>2.886,03</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>1737483</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>bmd 1737483.pdf</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>5.194,82</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>1737484</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>bmd 1737484.pdf</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>5.194,82</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>1740643</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>bmd 1740643.pdf</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>4.617,63</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>1741124</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>bmd 1741124.pdf</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>2.885,97</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>1741248</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>bmd 1741248.pdf</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>4.617,63</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
           <t>1726324</t>
         </is>
       </c>
-      <c r="B661" t="inlineStr">
-        <is>
-          <t>BMD</t>
-        </is>
-      </c>
-      <c r="C661" t="inlineStr">
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
         <is>
           <t>bmd parcial-1726324-hagap.pdf</t>
         </is>
       </c>
-      <c r="D661" t="inlineStr">
+      <c r="D673" t="inlineStr">
         <is>
           <t>2.048,89</t>
         </is>
       </c>
-      <c r="E661" t="inlineStr">
+      <c r="E673" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
